--- a/outputs/EVINV-POC-001/phase5/phase5-vv-matrix.xlsx
+++ b/outputs/EVINV-POC-001/phase5/phase5-vv-matrix.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 5 | Gate: 5 | Generated: 2026-08-18T21:25:55.190Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 5 | Gate: 5 | Generated: 2026-08-19T02:39:53.194Z</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         <v>Thermal test at rated load, 65°C coolant</v>
       </c>
       <c r="G9" t="str">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H9" t="str">
         <v>°C</v>
@@ -613,10 +613,10 @@
         <v>≤85°C at TP-CASE-1</v>
       </c>
       <c r="J9" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="K9" t="str">
-        <v>TEST-RPT-005-REVISED</v>
+        <v>TEST-RPT-005-FAIL</v>
       </c>
     </row>
     <row r="10">
